--- a/data/trans_orig/IP25A_R_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP25A_R_2023-Habitat-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión en 2023 (tasa de respuesta: 98,91%)</t>
+          <t>Menores según si emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión en 2023 (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15525</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9320</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>24319</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12,33%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,4%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>19,32%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>14347</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9297</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20687</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>12,59%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>18,15%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>18097</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10443</t>
+          <t>10156</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26378</t>
+          <t>21057</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>32443</t>
+          <t>30226</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23381</t>
+          <t>21877</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42781</t>
+          <t>40256</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>110381</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>101587</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>116586</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>87,67%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>80,68%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>92,6%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>99625</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>93285</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>104675</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>87,41%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>81,85%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>91,84%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>122315</t>
+          <t>103280</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>114034</t>
+          <t>96924</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>129969</t>
+          <t>107825</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>221941</t>
+          <t>213661</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>211603</t>
+          <t>203631</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>231003</t>
+          <t>222010</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>91,03%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>113972</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>113972</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>113972</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>117981</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>117981</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>117981</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>254384</t>
+          <t>243887</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>254384</t>
+          <t>243887</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>254384</t>
+          <t>243887</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>30633</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>21886</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>41974</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13,05%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17,88%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>22806</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>31859</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>12,08%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,47%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>16,88%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33023</t>
+          <t>21133</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23426</t>
+          <t>14536</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45840</t>
+          <t>29237</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>55830</t>
+          <t>51766</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43553</t>
+          <t>40910</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69398</t>
+          <t>65923</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>204119</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>192778</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>212866</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>86,95%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>82,12%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,68%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>165935</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>156882</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>172758</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>87,92%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,53%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>219412</t>
+          <t>161645</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>206595</t>
+          <t>153541</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>229009</t>
+          <t>168242</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>385346</t>
+          <t>365764</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>371778</t>
+          <t>351607</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>397623</t>
+          <t>376620</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>234752</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>234752</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>234752</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>276</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>188741</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>188741</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>188741</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>252435</t>
+          <t>182778</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>252435</t>
+          <t>182778</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>252435</t>
+          <t>182778</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>441176</t>
+          <t>417530</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>441176</t>
+          <t>417530</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>441176</t>
+          <t>417530</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>26157</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18331</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>34814</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15,54%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10,89%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20,68%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>34579</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19726</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>47727</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>18,59%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,61%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>25,66%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28282</t>
+          <t>29852</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20006</t>
+          <t>22074</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37914</t>
+          <t>39101</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>62861</t>
+          <t>56009</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45900</t>
+          <t>44443</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79212</t>
+          <t>69256</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>142184</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>133527</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>150010</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>84,46%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>79,32%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>89,11%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>151412</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>138264</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>166265</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>81,41%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>74,34%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>89,39%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>157004</t>
+          <t>122639</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147372</t>
+          <t>113390</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165280</t>
+          <t>130417</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>308416</t>
+          <t>264823</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>292065</t>
+          <t>251576</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>325377</t>
+          <t>276389</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>86,15%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>185991</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>185991</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>185991</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>152491</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>152491</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>152491</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371277</t>
+          <t>320832</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371277</t>
+          <t>320832</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371277</t>
+          <t>320832</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23695</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>16690</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>32370</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,03%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9,88%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>17998</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>11955</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>25191</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>10,88%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,22%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24924</t>
+          <t>18251</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17810</t>
+          <t>12010</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34457</t>
+          <t>25677</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>42922</t>
+          <t>41946</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32987</t>
+          <t>33116</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54592</t>
+          <t>52794</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>145207</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>136532</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>152212</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>85,97%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>80,84%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>90,12%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>147488</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>140295</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>153531</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>89,12%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,78%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,78%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>155737</t>
+          <t>146567</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>146204</t>
+          <t>139141</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>162851</t>
+          <t>152808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>303225</t>
+          <t>291775</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>291555</t>
+          <t>280927</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>313160</t>
+          <t>300605</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,08%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>165486</t>
+          <t>168902</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>165486</t>
+          <t>168902</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>165486</t>
+          <t>168902</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>180661</t>
+          <t>164818</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>180661</t>
+          <t>164818</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>180661</t>
+          <t>164818</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>346147</t>
+          <t>333721</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>346147</t>
+          <t>333721</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>346147</t>
+          <t>333721</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,62 +2092,62 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>96010</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>81248</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>112983</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13,76%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11,64%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>16,19%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>89730</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>72364</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>107420</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>13,72%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,06%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>16,42%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>104325</t>
+          <t>83936</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87401</t>
+          <t>71183</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>123075</t>
+          <t>99093</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>194055</t>
+          <t>179946</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>171524</t>
+          <t>159367</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>223073</t>
+          <t>204211</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -2205,67 +2205,67 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>601891</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>584918</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>616653</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>86,24%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>83,81%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>88,36%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>801</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>564459</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>546769</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>581825</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>86,28%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>83,58%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>88,94%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>840</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>654469</t>
+          <t>534132</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>635719</t>
+          <t>518975</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>671393</t>
+          <t>546885</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1218928</t>
+          <t>1136024</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1189910</t>
+          <t>1111759</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1241459</t>
+          <t>1156603</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,89%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>697901</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>697901</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>697901</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>926</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>654189</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>654189</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>654189</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>972</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>758794</t>
+          <t>618068</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>758794</t>
+          <t>618068</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>758794</t>
+          <t>618068</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1412983</t>
+          <t>1315970</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1412983</t>
+          <t>1315970</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1412983</t>
+          <t>1315970</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
